--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\joyin\workspace\BS-1.9\dev\branches\2.1.0sanqi\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView windowWidth="19890" windowHeight="7710"/>
   </bookViews>
   <sheets>
     <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
@@ -69,6 +64,9 @@
     <t>*代销机构所属监管机构</t>
   </si>
   <si>
+    <t>**产品代码</t>
+  </si>
+  <si>
     <t>**业务种类</t>
   </si>
   <si>
@@ -108,22 +106,10 @@
     <t>备注</t>
   </si>
   <si>
-    <t>110000 北京市</t>
-  </si>
-  <si>
-    <t>01 是</t>
-  </si>
-  <si>
-    <t>02 北京银保监局</t>
-  </si>
-  <si>
-    <t>01 募集期认购</t>
-  </si>
-  <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>05 网银</t>
+    <t>导入检查结果</t>
+  </si>
+  <si>
+    <t>数据状态</t>
   </si>
   <si>
     <t>业务明细信息登记模板填写说明</t>
@@ -143,7 +129,6 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“选择性粘贴”</t>
@@ -153,7 +138,6 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>并只</t>
@@ -163,7 +147,6 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“粘贴数值”</t>
@@ -179,6 +162,9 @@
     <t>关联账号开户所在地填写选项：</t>
   </si>
   <si>
+    <t>110000 北京市</t>
+  </si>
+  <si>
     <t>120000 天津市</t>
   </si>
   <si>
@@ -299,6 +285,9 @@
     <t>是否代销填写选项:</t>
   </si>
   <si>
+    <t>01 是</t>
+  </si>
+  <si>
     <t>02 否</t>
   </si>
   <si>
@@ -308,6 +297,9 @@
     <t>01 银保监会</t>
   </si>
   <si>
+    <t>02 北京银保监局</t>
+  </si>
+  <si>
     <t>03 上海银保监局</t>
   </si>
   <si>
@@ -416,6 +408,9 @@
     <t>业务种类填写选项:</t>
   </si>
   <si>
+    <t>01 募集期认购</t>
+  </si>
+  <si>
     <t>02 存续期申购</t>
   </si>
   <si>
@@ -467,6 +462,9 @@
     <t>币种</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -1011,6 +1009,9 @@
   </si>
   <si>
     <t>04 POS</t>
+  </si>
+  <si>
+    <t>05 网银</t>
   </si>
   <si>
     <t>06 手机银行</t>
@@ -1027,7 +1028,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.</t>
@@ -1037,7 +1037,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>0.0</t>
@@ -1052,22 +1051,20 @@
   <si>
     <t>1.新增业务明细信息登记模板</t>
   </si>
-  <si>
-    <t>导入检查结果</t>
-  </si>
-  <si>
-    <t>数据状态</t>
-  </si>
-  <si>
-    <t>**产品代码</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="0.00000_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1083,7 +1080,6 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1102,14 +1098,12 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1117,7 +1111,6 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1125,32 +1118,174 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="10"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1171,12 +1306,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1280,29 +1601,271 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="1" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1311,22 +1874,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1380,39 +1943,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2"/>
-    <cellStyle name="常规 2 2" xfId="1"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="常规 2 2" xfId="44"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="45" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="46" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="47" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="48" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="49" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="50"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1741,468 +2366,449 @@
       <a:lstStyle/>
     </a:spDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AC3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="22.75" style="32" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="18" style="32" customWidth="1" collapsed="1"/>
-    <col min="3" max="14" width="26.125" style="32" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="19.375" style="32" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="26.125" style="32" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="18.5" style="32" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="26.125" style="32" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="18.375" style="32" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="19.375" style="32" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="17.5" style="32" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="24" style="32" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="15.5" style="32" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="16.875" style="32" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="17.375" style="32" customWidth="1" collapsed="1"/>
-    <col min="28" max="29" width="18" style="31" customWidth="1"/>
-    <col min="30" max="30" width="9" style="33" collapsed="1"/>
-    <col min="31" max="31" width="9" style="33"/>
-    <col min="32" max="16384" width="9" style="33" collapsed="1"/>
+    <col min="1" max="1" width="22.75" style="30" customWidth="1"/>
+    <col min="2" max="2" width="18" style="30" customWidth="1"/>
+    <col min="3" max="14" width="26.125" style="30" customWidth="1"/>
+    <col min="15" max="16" width="19.375" style="30" customWidth="1"/>
+    <col min="17" max="18" width="26.125" style="30" customWidth="1"/>
+    <col min="19" max="19" width="18.5" style="30" customWidth="1"/>
+    <col min="20" max="20" width="26.125" style="31" customWidth="1"/>
+    <col min="21" max="21" width="18.375" style="31" customWidth="1"/>
+    <col min="22" max="22" width="19.375" style="32" customWidth="1"/>
+    <col min="23" max="23" width="17.5" style="32" customWidth="1"/>
+    <col min="24" max="24" width="24" style="31" customWidth="1"/>
+    <col min="25" max="25" width="15.5" style="30" customWidth="1"/>
+    <col min="26" max="26" width="16.875" style="30" customWidth="1"/>
+    <col min="27" max="27" width="17.375" style="30" customWidth="1"/>
+    <col min="28" max="29" width="18" style="33" customWidth="1"/>
+    <col min="30" max="16384" width="9" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="28" customFormat="1">
-      <c r="A1" s="29" t="s">
+    <row r="1" s="28" customFormat="1" spans="1:29">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="L1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="M1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="29" t="s">
-        <v>324</v>
-      </c>
-      <c r="O1" s="29" t="s">
+      <c r="N1" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="O1" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="29" t="s">
+      <c r="P1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="Q1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="R1" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="S1" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="29" t="s">
+      <c r="T1" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="29" t="s">
+      <c r="U1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="29" t="s">
+      <c r="V1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="29" t="s">
+      <c r="W1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="29" t="s">
+      <c r="X1" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="29" t="s">
+      <c r="Y1" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="29" t="s">
+      <c r="Z1" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="AC1" s="30" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" s="35" customFormat="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="34"/>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="34"/>
-      <c r="W3" s="34"/>
-      <c r="X3" s="34"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34"/>
-      <c r="AA3" s="34"/>
-      <c r="AB3" s="31"/>
-      <c r="AC3" s="31"/>
+      <c r="AA1" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="41" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" s="29" customFormat="1" spans="1:29">
+      <c r="A3" s="36"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="36"/>
+      <c r="AB3" s="33"/>
+      <c r="AC3" s="33"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <dataValidations count="4">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
+      <formula1>ywzl</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>填写说明!$A$48:$A$49</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
+      <formula1>填写说明!$A$7:$A$46</formula1>
+    </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:J1 M1 O1:P1 S1 Y1"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
+      <formula1>填写说明!$A$106:$A$141</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
+      <formula1>填写说明!$A$51:$A$87</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576">
       <formula1>bz</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
-      <formula1>ywzl</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
       <formula1>qd</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$7:$A$46</xm:f>
-          </x14:formula1>
-          <xm:sqref>I2:I1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$48:$A$49</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$51:$A$87</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$106:$A$141</xm:f>
-          </x14:formula1>
-          <xm:sqref>P2:P1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A329"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="73.375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75">
+    <row r="1" ht="15.75" spans="1:1">
       <c r="A1" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" ht="30" spans="1:1">
+      <c r="A2" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" spans="1:1">
+      <c r="A3" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" spans="1:1">
+      <c r="A4" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="30">
-      <c r="A2" s="7" t="s">
+    <row r="5" ht="15.75" spans="1:1">
+      <c r="A5" s="10"/>
+    </row>
+    <row r="6" ht="15.75" spans="1:1">
+      <c r="A6" s="11" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.75">
-      <c r="A3" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="15.75">
-      <c r="A4" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.75">
-      <c r="A5" s="10"/>
-    </row>
-    <row r="6" spans="1:1" ht="15.75">
-      <c r="A6" s="11" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="12" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="14" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="13" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -2387,92 +2993,92 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="19" t="s">
-        <v>29</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="19" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -2652,950 +3258,951 @@
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="19" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="19" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="19" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="19" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="19" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="19" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="20" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="20" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" s="20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="20" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="20" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="20" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="20" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="20" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" s="20" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="20" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="20" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="20" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="20" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="20" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="20" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="20" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" s="20" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="20" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="20" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="20" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="20" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="20" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="20" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="20" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="20" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="20" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="20" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" s="20" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="20" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="20" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="20" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="20" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="20" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="20" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="20" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="20" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" s="20" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="20" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="20" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="20" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" s="20" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" s="20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" s="20" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="20" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" s="20" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="20" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="20" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="20" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" s="20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="20" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" s="20" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="20" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" s="20" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="20" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" s="20" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" s="20" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="20" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="20" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="20" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="20" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" s="20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="20" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="20" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="20" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" s="20" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="20" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="20" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="20" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="20" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="20" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="20" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="20" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="20" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" s="20" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="20" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="20" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="20" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" s="20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="20" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" s="20" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" s="20" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" s="20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" s="20" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" s="20" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" s="20" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" s="20" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" s="20" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" s="20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" s="20" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" s="20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" s="20" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" s="20" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" s="20" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" s="20" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" s="20" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" s="20" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" s="20" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" s="20" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" s="20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" s="20" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" s="20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" s="20" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" s="22" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" s="23" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="323" spans="1:1">
       <c r="A323" s="24" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" s="25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" s="26" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="326" spans="1:1">
       <c r="A326" s="26" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="327" spans="1:1">
       <c r="A327" s="26" t="s">
-        <v>31</v>
+        <v>317</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328" s="26" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="329" spans="1:1">
       <c r="A329" s="27" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="34" customWidth="1" collapsed="1"/>
@@ -3603,31 +4210,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B2" s="3">
         <v>43761</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="29.1" customHeight="1">
+    <row r="3" ht="29.1" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19890" windowHeight="7710"/>
+    <workbookView windowWidth="20130" windowHeight="7710"/>
   </bookViews>
   <sheets>
     <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
@@ -1057,12 +1057,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="0.00000_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00000_ "/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -1122,10 +1122,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1137,23 +1153,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1167,7 +1167,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1181,9 +1197,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1198,76 +1267,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1285,7 +1285,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1312,7 +1312,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1324,7 +1324,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1336,13 +1342,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1360,115 +1366,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1486,13 +1384,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1602,27 +1596,34 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1647,25 +1648,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1685,17 +1683,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1707,10 +1701,10 @@
     <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1719,31 +1713,34 @@
     <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1752,103 +1749,100 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
@@ -1947,12 +1941,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1965,16 +1959,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2381,11 +2375,11 @@
     <col min="15" max="16" width="19.375" style="30" customWidth="1"/>
     <col min="17" max="18" width="26.125" style="30" customWidth="1"/>
     <col min="19" max="19" width="18.5" style="30" customWidth="1"/>
-    <col min="20" max="20" width="26.125" style="31" customWidth="1"/>
-    <col min="21" max="21" width="18.375" style="31" customWidth="1"/>
-    <col min="22" max="22" width="19.375" style="32" customWidth="1"/>
-    <col min="23" max="23" width="17.5" style="32" customWidth="1"/>
-    <col min="24" max="24" width="24" style="31" customWidth="1"/>
+    <col min="20" max="20" width="27.625" style="31" customWidth="1"/>
+    <col min="21" max="21" width="26.625" style="31" customWidth="1"/>
+    <col min="22" max="22" width="29.375" style="32" customWidth="1"/>
+    <col min="23" max="23" width="32.375" style="32" customWidth="1"/>
+    <col min="24" max="24" width="29.875" style="31" customWidth="1"/>
     <col min="25" max="25" width="15.5" style="30" customWidth="1"/>
     <col min="26" max="26" width="16.875" style="30" customWidth="1"/>
     <col min="27" max="27" width="17.375" style="30" customWidth="1"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\huaxia\code\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20130" windowHeight="7710"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20130" windowHeight="7710"/>
   </bookViews>
   <sheets>
     <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
@@ -1055,16 +1060,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00000_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1122,157 +1123,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color indexed="10"/>
       <name val="宋体"/>
@@ -1284,8 +1134,13 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1306,192 +1161,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1595,254 +1270,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
@@ -1853,13 +1286,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="1" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1868,22 +1301,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1975,63 +1408,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="常规 2 2" xfId="44"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="45" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="46" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="47" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="48" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="49" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="50"/>
+    <cellStyle name="常规 2" xfId="2"/>
+    <cellStyle name="常规 2 2" xfId="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2360,14 +1749,14 @@
       <a:lstStyle/>
     </a:spDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AC3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22.75" style="30" customWidth="1"/>
     <col min="2" max="2" width="18" style="30" customWidth="1"/>
@@ -2377,8 +1766,8 @@
     <col min="19" max="19" width="18.5" style="30" customWidth="1"/>
     <col min="20" max="20" width="27.625" style="31" customWidth="1"/>
     <col min="21" max="21" width="26.625" style="31" customWidth="1"/>
-    <col min="22" max="22" width="29.375" style="32" customWidth="1"/>
-    <col min="23" max="23" width="32.375" style="32" customWidth="1"/>
+    <col min="22" max="22" width="41.5" style="32" customWidth="1"/>
+    <col min="23" max="23" width="43" style="32" customWidth="1"/>
     <col min="24" max="24" width="29.875" style="31" customWidth="1"/>
     <col min="25" max="25" width="15.5" style="30" customWidth="1"/>
     <col min="26" max="26" width="16.875" style="30" customWidth="1"/>
@@ -2387,7 +1776,7 @@
     <col min="30" max="16384" width="9" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" s="28" customFormat="1" spans="1:29">
+    <row r="1" spans="1:29" s="28" customFormat="1">
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
@@ -2476,7 +1865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" s="29" customFormat="1" spans="1:29">
+    <row r="3" spans="1:29" s="29" customFormat="1">
       <c r="A3" s="36"/>
       <c r="B3" s="36"/>
       <c r="C3" s="36"/>
@@ -2508,23 +1897,12 @@
       <c r="AC3" s="33"/>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <phoneticPr fontId="11" type="noConversion"/>
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
       <formula1>ywzl</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
-      <formula1>填写说明!$A$48:$A$49</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
-      <formula1>填写说明!$A$7:$A$46</formula1>
-    </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:J1 M1 O1:P1 S1 Y1"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
-      <formula1>填写说明!$A$106:$A$141</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
-      <formula1>填写说明!$A$51:$A$87</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576">
       <formula1>bz</formula1>
     </dataValidation>
@@ -2532,45 +1910,73 @@
       <formula1>qd</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$48:$A$49</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$7:$A$46</xm:f>
+          </x14:formula1>
+          <xm:sqref>I2:I1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$106:$A$141</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$51:$A$87</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A329"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="73.375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:1">
+    <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" ht="30" spans="1:1">
+    <row r="2" spans="1:1" ht="30">
       <c r="A2" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="1:1">
+    <row r="3" spans="1:1" ht="15.75">
       <c r="A3" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:1">
+    <row r="4" spans="1:1" ht="15.75">
       <c r="A4" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" ht="15.75" spans="1:1">
+    <row r="5" spans="1:1" ht="15.75">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" ht="15.75" spans="1:1">
+    <row r="6" spans="1:1" ht="15.75">
       <c r="A6" s="11" t="s">
         <v>33</v>
       </c>
@@ -4186,17 +3592,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="34" customWidth="1" collapsed="1"/>
@@ -4218,7 +3623,7 @@
         <v>43761</v>
       </c>
     </row>
-    <row r="3" ht="29.1" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="29.1" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>323</v>
       </c>
@@ -4227,8 +3632,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20130" windowHeight="7710"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
     <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
@@ -69,9 +69,6 @@
     <t>*代销机构所属监管机构</t>
   </si>
   <si>
-    <t>**产品代码</t>
-  </si>
-  <si>
     <t>**业务种类</t>
   </si>
   <si>
@@ -111,10 +108,22 @@
     <t>备注</t>
   </si>
   <si>
-    <t>导入检查结果</t>
-  </si>
-  <si>
-    <t>数据状态</t>
+    <t>110000 北京市</t>
+  </si>
+  <si>
+    <t>01 是</t>
+  </si>
+  <si>
+    <t>02 北京银保监局</t>
+  </si>
+  <si>
+    <t>01 募集期认购</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>05 网银</t>
   </si>
   <si>
     <t>业务明细信息登记模板填写说明</t>
@@ -134,6 +143,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“选择性粘贴”</t>
@@ -143,6 +153,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>并只</t>
@@ -152,6 +163,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“粘贴数值”</t>
@@ -167,9 +179,6 @@
     <t>关联账号开户所在地填写选项：</t>
   </si>
   <si>
-    <t>110000 北京市</t>
-  </si>
-  <si>
     <t>120000 天津市</t>
   </si>
   <si>
@@ -290,9 +299,6 @@
     <t>是否代销填写选项:</t>
   </si>
   <si>
-    <t>01 是</t>
-  </si>
-  <si>
     <t>02 否</t>
   </si>
   <si>
@@ -302,9 +308,6 @@
     <t>01 银保监会</t>
   </si>
   <si>
-    <t>02 北京银保监局</t>
-  </si>
-  <si>
     <t>03 上海银保监局</t>
   </si>
   <si>
@@ -413,9 +416,6 @@
     <t>业务种类填写选项:</t>
   </si>
   <si>
-    <t>01 募集期认购</t>
-  </si>
-  <si>
     <t>02 存续期申购</t>
   </si>
   <si>
@@ -467,9 +467,6 @@
     <t>币种</t>
   </si>
   <si>
-    <t>CNY</t>
-  </si>
-  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -1014,9 +1011,6 @@
   </si>
   <si>
     <t>04 POS</t>
-  </si>
-  <si>
-    <t>05 网银</t>
   </si>
   <si>
     <t>06 手机银行</t>
@@ -1033,6 +1027,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.</t>
@@ -1042,6 +1037,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>0.0</t>
@@ -1055,17 +1051,23 @@
   </si>
   <si>
     <t>1.新增业务明细信息登记模板</t>
+  </si>
+  <si>
+    <t>导入检查结果</t>
+  </si>
+  <si>
+    <t>数据状态</t>
+  </si>
+  <si>
+    <t>**产品代码</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0.00000_ "/>
-  </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1081,6 +1083,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1099,12 +1102,14 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1112,6 +1117,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1119,6 +1125,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1126,16 +1133,24 @@
       <sz val="12"/>
       <color indexed="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1161,7 +1176,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39994506668294322"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1278,11 +1293,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1370,43 +1385,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1755,166 +1752,174 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.75" style="30" customWidth="1"/>
-    <col min="2" max="2" width="18" style="30" customWidth="1"/>
-    <col min="3" max="14" width="26.125" style="30" customWidth="1"/>
-    <col min="15" max="16" width="19.375" style="30" customWidth="1"/>
-    <col min="17" max="18" width="26.125" style="30" customWidth="1"/>
-    <col min="19" max="19" width="18.5" style="30" customWidth="1"/>
-    <col min="20" max="20" width="27.625" style="31" customWidth="1"/>
-    <col min="21" max="21" width="26.625" style="31" customWidth="1"/>
-    <col min="22" max="22" width="41.5" style="32" customWidth="1"/>
-    <col min="23" max="23" width="43" style="32" customWidth="1"/>
-    <col min="24" max="24" width="29.875" style="31" customWidth="1"/>
-    <col min="25" max="25" width="15.5" style="30" customWidth="1"/>
-    <col min="26" max="26" width="16.875" style="30" customWidth="1"/>
-    <col min="27" max="27" width="17.375" style="30" customWidth="1"/>
-    <col min="28" max="29" width="18" style="33" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="34"/>
+    <col min="1" max="1" width="22.75" style="32" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18" style="32" customWidth="1" collapsed="1"/>
+    <col min="3" max="14" width="26.125" style="32" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="19.375" style="32" customWidth="1" collapsed="1"/>
+    <col min="17" max="18" width="26.125" style="32" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="18.5" style="32" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" width="26.125" style="32" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="18.375" style="32" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="30" style="32" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="34.625" style="32" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="24" style="32" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="15.5" style="32" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="16.875" style="32" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="17.375" style="32" customWidth="1" collapsed="1"/>
+    <col min="28" max="29" width="18" style="31" customWidth="1"/>
+    <col min="30" max="30" width="9" style="33" collapsed="1"/>
+    <col min="31" max="31" width="9" style="33"/>
+    <col min="32" max="16384" width="9" style="33" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="28" customFormat="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="J1" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="L1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="M1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="35" t="s">
+      <c r="N1" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="O1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="35" t="s">
+      <c r="P1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="35" t="s">
+      <c r="Q1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="35" t="s">
+      <c r="R1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="35" t="s">
+      <c r="S1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="T1" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="37" t="s">
+      <c r="U1" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="37" t="s">
+      <c r="V1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="38" t="s">
+      <c r="W1" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="38" t="s">
+      <c r="X1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="37" t="s">
+      <c r="Y1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="35" t="s">
+      <c r="Z1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="35" t="s">
+      <c r="AA1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="41" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" s="29" customFormat="1">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="36"/>
-      <c r="AB3" s="33"/>
-      <c r="AC3" s="33"/>
+      <c r="AB1" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="AC1" s="30" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" s="35" customFormat="1">
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="34"/>
+      <c r="AA2" s="34"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
-      <formula1>ywzl</formula1>
-    </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:J1 M1 O1:P1 S1 Y1"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576">
       <formula1>bz</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
+      <formula1>ywzl</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
       <formula1>qd</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$7:$A$46</xm:f>
+          </x14:formula1>
+          <xm:sqref>I2:I1048576</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$48:$A$49</xm:f>
@@ -1923,21 +1928,15 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>填写说明!$A$7:$A$46</xm:f>
+            <xm:f>填写说明!$A$51:$A$87</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I1048576</xm:sqref>
+          <xm:sqref>M2:M1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$106:$A$141</xm:f>
           </x14:formula1>
           <xm:sqref>P2:P1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$51:$A$87</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1955,22 +1954,22 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="30">
       <c r="A2" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.75">
       <c r="A3" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.75">
       <c r="A4" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.75">
@@ -1978,237 +1977,237 @@
     </row>
     <row r="6" spans="1:1" ht="15.75">
       <c r="A6" s="11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="12" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="14" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="13" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -2393,92 +2392,92 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="19" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="19" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -2658,937 +2657,937 @@
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="19" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="19" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="19" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="19" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="19" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="20" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="20" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" s="20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="20" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="20" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="20" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="20" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="20" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="20" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="20" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="20" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="20" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="20" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="20" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="20" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="20" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="20" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" s="20" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="20" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="20" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="20" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="20" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" s="20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" s="20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" s="20" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="20" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" s="20" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" s="20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" s="20" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="20" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="20" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" s="20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="20" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="20" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="20" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="20" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="20" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="20" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" s="20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="20" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="20" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" s="20" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="20" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="20" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" s="20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="20" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="20" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="20" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" s="20" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="20" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" s="20" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" s="20" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" s="20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" s="20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" s="20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" s="20" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" s="20" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" s="20" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" s="20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" s="20" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" s="20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" s="20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" s="20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" s="20" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" s="20" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" s="20" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" s="20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" s="20" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" s="20" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" s="22" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="323" spans="1:1">
       <c r="A323" s="24" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" s="25" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" s="26" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="326" spans="1:1">
       <c r="A326" s="26" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="327" spans="1:1">
       <c r="A327" s="26" t="s">
-        <v>317</v>
+        <v>31</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328" s="26" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="329" spans="1:1">
       <c r="A329" s="27" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3609,15 +3608,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B2" s="3">
         <v>43761</v>
@@ -3625,10 +3624,10 @@
     </row>
     <row r="3" spans="1:2" ht="29.1" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\huaxia\code\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\huaxia\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1067,6 +1067,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00000_ "/>
+  </numFmts>
   <fonts count="13">
     <font>
       <sz val="12"/>
@@ -1297,7 +1300,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1404,6 +1407,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1764,7 +1776,7 @@
     <col min="20" max="20" width="26.125" style="32" customWidth="1" collapsed="1"/>
     <col min="21" max="21" width="18.375" style="32" customWidth="1" collapsed="1"/>
     <col min="22" max="22" width="30" style="32" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="34.625" style="32" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="34.625" style="38" customWidth="1" collapsed="1"/>
     <col min="24" max="24" width="24" style="32" customWidth="1" collapsed="1"/>
     <col min="25" max="25" width="15.5" style="32" customWidth="1" collapsed="1"/>
     <col min="26" max="26" width="16.875" style="32" customWidth="1" collapsed="1"/>
@@ -1842,7 +1854,7 @@
       <c r="V1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="29" t="s">
+      <c r="W1" s="36" t="s">
         <v>21</v>
       </c>
       <c r="X1" s="29" t="s">
@@ -1887,7 +1899,7 @@
       <c r="T2" s="34"/>
       <c r="U2" s="34"/>
       <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
+      <c r="W2" s="37"/>
       <c r="X2" s="34"/>
       <c r="Y2" s="34"/>
       <c r="Z2" s="34"/>
